--- a/artfynd/A 27506-2026 artfynd.xlsx
+++ b/artfynd/A 27506-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109182223</v>
+        <v>134434100</v>
       </c>
       <c r="B2" t="n">
-        <v>98972</v>
+        <v>92220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223591</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jassa, 450 m V toppen, Nb</t>
+          <t>Kaarnevaara, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>851537</v>
+        <v>851719</v>
       </c>
       <c r="R2" t="n">
-        <v>7520432</v>
+        <v>7520258</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1997-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1997-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Norrbottens flora - 2010.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,72 +766,67 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>gles skog</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Frantz Hopkins, Lotta Wallin</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Norrbottens flora 2010</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109187076</v>
+        <v>134434099</v>
       </c>
       <c r="B3" t="n">
-        <v>99076</v>
+        <v>93265</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jassa, 400 m SV toppen, Nb</t>
+          <t>Kaarnevaara, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>851639</v>
+        <v>851713</v>
       </c>
       <c r="R3" t="n">
-        <v>7520234</v>
+        <v>7520266</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,17 +850,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1997-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1997-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Norrbottens flora - 2010.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -873,239 +872,18 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>fuktig skog</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Frantz Hopkins, Lotta Wallin</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Norrbottens flora 2010</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>134434100</v>
-      </c>
-      <c r="B4" t="n">
-        <v>92213</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>65</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Fläckporing</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Anthoporia albobrunnea</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Kaarnevaara, Nb</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>851719</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7520258</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Pajala</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Pajala</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>134434099</v>
-      </c>
-      <c r="B5" t="n">
-        <v>93258</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>4362</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Blå taggsvamp</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Hydnellum caeruleum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Kaarnevaara, Nb</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>851713</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7520266</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Pajala</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Pajala</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
